--- a/extra/report/No.課題2_テスト結果.xlsx
+++ b/extra/report/No.課題2_テスト結果.xlsx
@@ -3,9 +3,9 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="20417"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B8F4EE0B-BE7E-48C9-A306-F77892D7AD62}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E9D7578B-7E22-43A5-AF0C-CDAFC901A319}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="105" windowWidth="14805" windowHeight="8010" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="240" yWindow="105" windowWidth="14805" windowHeight="8010" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="前提" sheetId="2" r:id="rId1"/>
@@ -19,11 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17" uniqueCount="12">
-  <si>
-    <t>管理者アカウントでログイン済み</t>
-    <phoneticPr fontId="1"/>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15" uniqueCount="10">
   <si>
     <t>【前提】</t>
     <rPh sb="1" eb="3">
@@ -32,48 +28,7 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>ログインが成功するとトップ画面に遷移する</t>
-    <rPh sb="5" eb="7">
-      <t>セイコウ</t>
-    </rPh>
-    <rPh sb="13" eb="15">
-      <t>ガメン</t>
-    </rPh>
-    <rPh sb="16" eb="18">
-      <t>センイ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>1.「メールアドレス」「氏名」両方空欄で検索ボタン押下</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>加入者情報管理を押下すると加入者情報管理画面に遷移する</t>
-    <rPh sb="0" eb="3">
-      <t>カニュウシャ</t>
-    </rPh>
-    <rPh sb="3" eb="5">
-      <t>ジョウホウ</t>
-    </rPh>
-    <rPh sb="5" eb="7">
-      <t>カンリ</t>
-    </rPh>
-    <rPh sb="8" eb="10">
-      <t>オウカ</t>
-    </rPh>
-    <rPh sb="13" eb="16">
-      <t>カニュウシャ</t>
-    </rPh>
-    <rPh sb="16" eb="18">
-      <t>ジョウホウ</t>
-    </rPh>
-    <rPh sb="18" eb="22">
-      <t>カンリガメン</t>
-    </rPh>
-    <rPh sb="23" eb="25">
-      <t>センイ</t>
-    </rPh>
     <phoneticPr fontId="1"/>
   </si>
   <si>
@@ -104,16 +59,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>データーベースに登録済みのユーザー情報が表示される</t>
-    <rPh sb="8" eb="11">
-      <t>トウロクズ</t>
-    </rPh>
-    <rPh sb="20" eb="22">
-      <t>ヒョウジ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>3.「メールアドレス」空欄「氏名」入力ありで検索ボタン押下</t>
     <phoneticPr fontId="1"/>
   </si>
@@ -123,6 +68,20 @@
   </si>
   <si>
     <t>4.「メールアドレス」「氏名」両方入力ありで検索ボタン押下</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>管理者アカウント(user)でログイン済み</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>データーベースのT_MEMBERテーブルに以下のユーザー情報が入っている</t>
+    <rPh sb="21" eb="23">
+      <t>イカ</t>
+    </rPh>
+    <rPh sb="31" eb="32">
+      <t>ハイ</t>
+    </rPh>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -207,81 +166,25 @@
 
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>4</xdr:col>
-      <xdr:colOff>549519</xdr:colOff>
-      <xdr:row>12</xdr:row>
-      <xdr:rowOff>95250</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>4</xdr:col>
-      <xdr:colOff>549521</xdr:colOff>
-      <xdr:row>16</xdr:row>
-      <xdr:rowOff>146538</xdr:rowOff>
-    </xdr:to>
-    <xdr:cxnSp macro="">
-      <xdr:nvCxnSpPr>
-        <xdr:cNvPr id="18" name="直線矢印コネクタ 17">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{9DC475BD-916F-4844-919B-A1C0027C6238}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvCxnSpPr/>
-      </xdr:nvCxnSpPr>
-      <xdr:spPr>
-        <a:xfrm flipH="1">
-          <a:off x="3304442" y="2117481"/>
-          <a:ext cx="2" cy="725365"/>
-        </a:xfrm>
-        <a:prstGeom prst="straightConnector1">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:ln w="38100">
-          <a:solidFill>
-            <a:srgbClr val="FF0000"/>
-          </a:solidFill>
-          <a:tailEnd type="triangle"/>
-        </a:ln>
-      </xdr:spPr>
-      <xdr:style>
-        <a:lnRef idx="1">
-          <a:schemeClr val="accent1"/>
-        </a:lnRef>
-        <a:fillRef idx="0">
-          <a:schemeClr val="accent1"/>
-        </a:fillRef>
-        <a:effectRef idx="0">
-          <a:schemeClr val="accent1"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="tx1"/>
-        </a:fontRef>
-      </xdr:style>
-    </xdr:cxnSp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>674077</xdr:colOff>
-      <xdr:row>4</xdr:row>
-      <xdr:rowOff>161192</xdr:rowOff>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>7</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>15</xdr:col>
-      <xdr:colOff>401515</xdr:colOff>
-      <xdr:row>13</xdr:row>
-      <xdr:rowOff>63802</xdr:rowOff>
+      <xdr:colOff>7941</xdr:colOff>
+      <xdr:row>15</xdr:row>
+      <xdr:rowOff>166533</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="29" name="図 28">
+        <xdr:cNvPr id="3" name="図 2">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{BBA6DA1D-72C4-4CAD-B9D8-DA4E99D0955D}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{03AFA900-8705-4716-84A6-64B91C0FDDE4}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -290,7 +193,7 @@
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1" cstate="print">
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1">
           <a:extLst>
             <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
               <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
@@ -303,358 +206,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="674077" y="835269"/>
-          <a:ext cx="10058400" cy="1419283"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>4</xdr:col>
-      <xdr:colOff>277692</xdr:colOff>
-      <xdr:row>11</xdr:row>
-      <xdr:rowOff>87921</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>5</xdr:col>
-      <xdr:colOff>96717</xdr:colOff>
-      <xdr:row>12</xdr:row>
-      <xdr:rowOff>126021</xdr:rowOff>
-    </xdr:to>
-    <xdr:sp macro="" textlink="">
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="16" name="正方形/長方形 15">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{213F3985-71AF-4B32-8926-E72FC35D4D1D}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvSpPr/>
-      </xdr:nvSpPr>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="3032615" y="1941633"/>
-          <a:ext cx="507756" cy="206619"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-        <a:ln w="38100" cap="flat" cmpd="sng" algn="ctr">
-          <a:solidFill>
-            <a:srgbClr val="FF0000"/>
-          </a:solidFill>
-          <a:prstDash val="solid"/>
-          <a:round/>
-          <a:headEnd type="none" w="med" len="med"/>
-          <a:tailEnd type="none" w="med" len="med"/>
-        </a:ln>
-      </xdr:spPr>
-      <xdr:style>
-        <a:lnRef idx="0">
-          <a:scrgbClr r="0" g="0" b="0"/>
-        </a:lnRef>
-        <a:fillRef idx="0">
-          <a:scrgbClr r="0" g="0" b="0"/>
-        </a:fillRef>
-        <a:effectRef idx="0">
-          <a:scrgbClr r="0" g="0" b="0"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="accent2"/>
-        </a:fontRef>
-      </xdr:style>
-      <xdr:txBody>
-        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
-        <a:lstStyle/>
-        <a:p>
-          <a:pPr algn="l"/>
-          <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100">
-            <a:solidFill>
-              <a:srgbClr val="FF0000"/>
-            </a:solidFill>
-          </a:endParaRPr>
-        </a:p>
-      </xdr:txBody>
-    </xdr:sp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>681404</xdr:colOff>
-      <xdr:row>19</xdr:row>
-      <xdr:rowOff>7327</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>15</xdr:col>
-      <xdr:colOff>408842</xdr:colOff>
-      <xdr:row>26</xdr:row>
-      <xdr:rowOff>161129</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="32" name="図 31">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{1485F59F-3C9E-4AED-9A83-C2BA5FFD7C40}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2" cstate="print">
-          <a:extLst>
-            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
-              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
-            </a:ext>
-          </a:extLst>
-        </a:blip>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="681404" y="3209192"/>
-          <a:ext cx="10058400" cy="1333437"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>2</xdr:col>
-      <xdr:colOff>468922</xdr:colOff>
-      <xdr:row>19</xdr:row>
-      <xdr:rowOff>102577</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>410308</xdr:colOff>
-      <xdr:row>21</xdr:row>
-      <xdr:rowOff>14653</xdr:rowOff>
-    </xdr:to>
-    <xdr:sp macro="" textlink="">
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="22" name="正方形/長方形 21">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{0F6AD45D-3A7E-4ADE-9992-F486FAC7AE70}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvSpPr/>
-      </xdr:nvSpPr>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="1846384" y="3304442"/>
-          <a:ext cx="630116" cy="249115"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-        <a:ln w="38100" cap="flat" cmpd="sng" algn="ctr">
-          <a:solidFill>
-            <a:srgbClr val="FF0000"/>
-          </a:solidFill>
-          <a:prstDash val="solid"/>
-          <a:round/>
-          <a:headEnd type="none" w="med" len="med"/>
-          <a:tailEnd type="none" w="med" len="med"/>
-        </a:ln>
-      </xdr:spPr>
-      <xdr:style>
-        <a:lnRef idx="0">
-          <a:scrgbClr r="0" g="0" b="0"/>
-        </a:lnRef>
-        <a:fillRef idx="0">
-          <a:scrgbClr r="0" g="0" b="0"/>
-        </a:fillRef>
-        <a:effectRef idx="0">
-          <a:scrgbClr r="0" g="0" b="0"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="accent2"/>
-        </a:fontRef>
-      </xdr:style>
-      <xdr:txBody>
-        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
-        <a:lstStyle/>
-        <a:p>
-          <a:pPr algn="l"/>
-          <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100">
-            <a:solidFill>
-              <a:srgbClr val="FF0000"/>
-            </a:solidFill>
-          </a:endParaRPr>
-        </a:p>
-      </xdr:txBody>
-    </xdr:sp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>87923</xdr:colOff>
-      <xdr:row>21</xdr:row>
-      <xdr:rowOff>65941</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>95251</xdr:colOff>
-      <xdr:row>29</xdr:row>
-      <xdr:rowOff>146538</xdr:rowOff>
-    </xdr:to>
-    <xdr:cxnSp macro="">
-      <xdr:nvCxnSpPr>
-        <xdr:cNvPr id="24" name="直線矢印コネクタ 23">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{6EB43BCD-C4DB-4347-BDED-91EDED3DD70F}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvCxnSpPr/>
-      </xdr:nvCxnSpPr>
-      <xdr:spPr>
-        <a:xfrm flipH="1">
-          <a:off x="2154115" y="3604845"/>
-          <a:ext cx="7328" cy="1428751"/>
-        </a:xfrm>
-        <a:prstGeom prst="straightConnector1">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:ln w="38100">
-          <a:solidFill>
-            <a:srgbClr val="FF0000"/>
-          </a:solidFill>
-          <a:tailEnd type="triangle"/>
-        </a:ln>
-      </xdr:spPr>
-      <xdr:style>
-        <a:lnRef idx="1">
-          <a:schemeClr val="accent1"/>
-        </a:lnRef>
-        <a:fillRef idx="0">
-          <a:schemeClr val="accent1"/>
-        </a:fillRef>
-        <a:effectRef idx="0">
-          <a:schemeClr val="accent1"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="tx1"/>
-        </a:fontRef>
-      </xdr:style>
-    </xdr:cxnSp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>32</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>15</xdr:col>
-      <xdr:colOff>416169</xdr:colOff>
-      <xdr:row>41</xdr:row>
-      <xdr:rowOff>58937</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="38" name="図 37">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{7C56E306-5F16-42CA-8A17-F03B12AAB316}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3" cstate="print">
-          <a:extLst>
-            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
-              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
-            </a:ext>
-          </a:extLst>
-        </a:blip>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="688731" y="5392615"/>
-          <a:ext cx="10058400" cy="1575610"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>46</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>14</xdr:col>
-      <xdr:colOff>363250</xdr:colOff>
-      <xdr:row>54</xdr:row>
-      <xdr:rowOff>109375</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="4" name="図 3">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{A90EA933-EB11-4724-9227-C08C662F145D}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId4">
-          <a:extLst>
-            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
-              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
-            </a:ext>
-          </a:extLst>
-        </a:blip>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="688731" y="7751885"/>
-          <a:ext cx="9316750" cy="1457528"/>
+          <a:off x="688731" y="1179635"/>
+          <a:ext cx="9650172" cy="1514686"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -894,56 +447,6 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>19707</xdr:colOff>
-      <xdr:row>26</xdr:row>
-      <xdr:rowOff>157655</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>37</xdr:col>
-      <xdr:colOff>145832</xdr:colOff>
-      <xdr:row>39</xdr:row>
-      <xdr:rowOff>32353</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="12" name="図 11">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{85BC135E-361A-4DF2-ADA8-F9CC59841621}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3" cstate="print">
-          <a:extLst>
-            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
-              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
-            </a:ext>
-          </a:extLst>
-        </a:blip>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="295604" y="4598276"/>
-          <a:ext cx="10058400" cy="2095008"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
       <xdr:col>38</xdr:col>
       <xdr:colOff>13138</xdr:colOff>
       <xdr:row>26</xdr:row>
@@ -969,7 +472,7 @@
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId4">
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3">
           <a:extLst>
             <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
               <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
@@ -984,6 +487,56 @@
         <a:xfrm>
           <a:off x="10497207" y="4591708"/>
           <a:ext cx="3844385" cy="5478986"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>26</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>37</xdr:col>
+      <xdr:colOff>126125</xdr:colOff>
+      <xdr:row>50</xdr:row>
+      <xdr:rowOff>168166</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="4" name="図 3">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{AF43BD1E-6863-4A39-B8CB-C0063C572F0D}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId4">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="275897" y="4440621"/>
+          <a:ext cx="10058400" cy="4267200"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -1023,8 +576,8 @@
         </a:xfrm>
         <a:prstGeom prst="wedgeRectCallout">
           <a:avLst>
-            <a:gd name="adj1" fmla="val -36421"/>
-            <a:gd name="adj2" fmla="val 68789"/>
+            <a:gd name="adj1" fmla="val -32062"/>
+            <a:gd name="adj2" fmla="val 80501"/>
           </a:avLst>
         </a:prstGeom>
       </xdr:spPr>
@@ -1382,23 +935,23 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>6569</xdr:colOff>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>683172</xdr:colOff>
       <xdr:row>27</xdr:row>
-      <xdr:rowOff>19707</xdr:rowOff>
+      <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>15</xdr:col>
-      <xdr:colOff>500555</xdr:colOff>
-      <xdr:row>38</xdr:row>
-      <xdr:rowOff>157379</xdr:rowOff>
+      <xdr:colOff>493986</xdr:colOff>
+      <xdr:row>46</xdr:row>
+      <xdr:rowOff>110</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="11" name="図 10">
+        <xdr:cNvPr id="4" name="図 3">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{3478F6D2-C06D-4D9C-9DCC-E0C7E1AC33CC}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{63A0802D-AD27-4054-A764-1CBCBCFD5122}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1407,7 +960,7 @@
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId4" cstate="print">
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId4">
           <a:extLst>
             <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
               <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
@@ -1420,8 +973,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="689741" y="4631121"/>
-          <a:ext cx="10058400" cy="2016396"/>
+          <a:off x="683172" y="4611414"/>
+          <a:ext cx="10058400" cy="3245179"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -1689,56 +1242,6 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>683172</xdr:colOff>
-      <xdr:row>26</xdr:row>
-      <xdr:rowOff>6569</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>15</xdr:col>
-      <xdr:colOff>493986</xdr:colOff>
-      <xdr:row>36</xdr:row>
-      <xdr:rowOff>587</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="7" name="図 6">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{806FDD9E-5007-4DCB-82EE-554046F924ED}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3" cstate="print">
-          <a:extLst>
-            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
-              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
-            </a:ext>
-          </a:extLst>
-        </a:blip>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="683172" y="4447190"/>
-          <a:ext cx="10058400" cy="1701949"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
       <xdr:col>17</xdr:col>
       <xdr:colOff>0</xdr:colOff>
       <xdr:row>26</xdr:row>
@@ -1764,7 +1267,7 @@
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId4">
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3">
           <a:extLst>
             <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
               <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
@@ -1785,190 +1288,6 @@
         </a:prstGeom>
       </xdr:spPr>
     </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>7</xdr:col>
-      <xdr:colOff>485774</xdr:colOff>
-      <xdr:row>23</xdr:row>
-      <xdr:rowOff>47626</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>12</xdr:col>
-      <xdr:colOff>430695</xdr:colOff>
-      <xdr:row>27</xdr:row>
-      <xdr:rowOff>66261</xdr:rowOff>
-    </xdr:to>
-    <xdr:sp macro="" textlink="">
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="10" name="吹き出し: 四角形 9">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{27A5471B-65C7-40E9-884A-D40DF40F3E20}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvSpPr/>
-      </xdr:nvSpPr>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="5297970" y="4048126"/>
-          <a:ext cx="3382203" cy="714374"/>
-        </a:xfrm>
-        <a:prstGeom prst="wedgeRectCallout">
-          <a:avLst>
-            <a:gd name="adj1" fmla="val -36321"/>
-            <a:gd name="adj2" fmla="val 102226"/>
-          </a:avLst>
-        </a:prstGeom>
-      </xdr:spPr>
-      <xdr:style>
-        <a:lnRef idx="2">
-          <a:schemeClr val="accent1"/>
-        </a:lnRef>
-        <a:fillRef idx="1">
-          <a:schemeClr val="lt1"/>
-        </a:fillRef>
-        <a:effectRef idx="0">
-          <a:schemeClr val="accent1"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="dk1"/>
-        </a:fontRef>
-      </xdr:style>
-      <xdr:txBody>
-        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
-        <a:lstStyle/>
-        <a:p>
-          <a:pPr algn="l"/>
-          <a:r>
-            <a:rPr lang="en-US" altLang="ja-JP" sz="1100">
-              <a:solidFill>
-                <a:schemeClr val="dk1"/>
-              </a:solidFill>
-              <a:effectLst/>
-              <a:latin typeface="+mn-lt"/>
-              <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="+mn-cs"/>
-            </a:rPr>
-            <a:t>NO.3</a:t>
-          </a:r>
-          <a:r>
-            <a:rPr lang="ja-JP" altLang="ja-JP" sz="1100">
-              <a:solidFill>
-                <a:schemeClr val="dk1"/>
-              </a:solidFill>
-              <a:effectLst/>
-              <a:latin typeface="+mn-lt"/>
-              <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="+mn-cs"/>
-            </a:rPr>
-            <a:t>「氏名」のみに</a:t>
-          </a:r>
-          <a:r>
-            <a:rPr lang="en-US" altLang="ja-JP" sz="1100">
-              <a:solidFill>
-                <a:schemeClr val="dk1"/>
-              </a:solidFill>
-              <a:effectLst/>
-              <a:latin typeface="+mn-lt"/>
-              <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="+mn-cs"/>
-            </a:rPr>
-            <a:t>”</a:t>
-          </a:r>
-          <a:r>
-            <a:rPr lang="ja-JP" altLang="ja-JP" sz="1100">
-              <a:solidFill>
-                <a:schemeClr val="dk1"/>
-              </a:solidFill>
-              <a:effectLst/>
-              <a:latin typeface="+mn-lt"/>
-              <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="+mn-cs"/>
-            </a:rPr>
-            <a:t>山田</a:t>
-          </a:r>
-          <a:r>
-            <a:rPr lang="en-US" altLang="ja-JP" sz="1100">
-              <a:solidFill>
-                <a:schemeClr val="dk1"/>
-              </a:solidFill>
-              <a:effectLst/>
-              <a:latin typeface="+mn-lt"/>
-              <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="+mn-cs"/>
-            </a:rPr>
-            <a:t>”</a:t>
-          </a:r>
-          <a:r>
-            <a:rPr lang="ja-JP" altLang="ja-JP" sz="1100">
-              <a:solidFill>
-                <a:schemeClr val="dk1"/>
-              </a:solidFill>
-              <a:effectLst/>
-              <a:latin typeface="+mn-lt"/>
-              <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="+mn-cs"/>
-            </a:rPr>
-            <a:t>と入力して検索ボタンを押下したとき、</a:t>
-          </a:r>
-          <a:r>
-            <a:rPr lang="en-US" altLang="ja-JP" sz="1100">
-              <a:solidFill>
-                <a:schemeClr val="dk1"/>
-              </a:solidFill>
-              <a:effectLst/>
-              <a:latin typeface="+mn-lt"/>
-              <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="+mn-cs"/>
-            </a:rPr>
-            <a:t>”</a:t>
-          </a:r>
-          <a:r>
-            <a:rPr lang="ja-JP" altLang="ja-JP" sz="1100">
-              <a:solidFill>
-                <a:schemeClr val="dk1"/>
-              </a:solidFill>
-              <a:effectLst/>
-              <a:latin typeface="+mn-lt"/>
-              <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="+mn-cs"/>
-            </a:rPr>
-            <a:t>山田</a:t>
-          </a:r>
-          <a:r>
-            <a:rPr lang="en-US" altLang="ja-JP" sz="1100">
-              <a:solidFill>
-                <a:schemeClr val="dk1"/>
-              </a:solidFill>
-              <a:effectLst/>
-              <a:latin typeface="+mn-lt"/>
-              <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="+mn-cs"/>
-            </a:rPr>
-            <a:t>”</a:t>
-          </a:r>
-          <a:r>
-            <a:rPr lang="ja-JP" altLang="ja-JP" sz="1100">
-              <a:solidFill>
-                <a:schemeClr val="dk1"/>
-              </a:solidFill>
-              <a:effectLst/>
-              <a:latin typeface="+mn-lt"/>
-              <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="+mn-cs"/>
-            </a:rPr>
-            <a:t>と部分一致した氏名を持つユーザーの情報が表示される</a:t>
-          </a:r>
-          <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100">
-            <a:latin typeface="+mn-ea"/>
-            <a:ea typeface="+mn-ea"/>
-          </a:endParaRPr>
-        </a:p>
-      </xdr:txBody>
-    </xdr:sp>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
@@ -2095,6 +1414,240 @@
     </xdr:cxnSp>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>683172</xdr:colOff>
+      <xdr:row>26</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>15</xdr:col>
+      <xdr:colOff>493986</xdr:colOff>
+      <xdr:row>43</xdr:row>
+      <xdr:rowOff>109059</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="4" name="図 3">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{E73B12BA-593C-4D1B-893B-1DF1CFDED4A0}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId4">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="683172" y="4440621"/>
+          <a:ext cx="10058400" cy="3012541"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>485774</xdr:colOff>
+      <xdr:row>23</xdr:row>
+      <xdr:rowOff>47626</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>12</xdr:col>
+      <xdr:colOff>430695</xdr:colOff>
+      <xdr:row>27</xdr:row>
+      <xdr:rowOff>66261</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="10" name="吹き出し: 四角形 9">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{27A5471B-65C7-40E9-884A-D40DF40F3E20}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="5297970" y="4048126"/>
+          <a:ext cx="3382203" cy="714374"/>
+        </a:xfrm>
+        <a:prstGeom prst="wedgeRectCallout">
+          <a:avLst>
+            <a:gd name="adj1" fmla="val -36321"/>
+            <a:gd name="adj2" fmla="val 102226"/>
+          </a:avLst>
+        </a:prstGeom>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="lt1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="dk1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr lang="en-US" altLang="ja-JP" sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>NO.3</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="ja-JP" altLang="ja-JP" sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>「氏名」のみに</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" altLang="ja-JP" sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>”</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="ja-JP" altLang="ja-JP" sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>山田</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" altLang="ja-JP" sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>”</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="ja-JP" altLang="ja-JP" sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>と入力して検索ボタンを押下したとき、</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" altLang="ja-JP" sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>”</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="ja-JP" altLang="ja-JP" sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>山田</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" altLang="ja-JP" sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>”</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="ja-JP" altLang="ja-JP" sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>と部分一致した氏名を持つユーザーの情報が表示される</a:t>
+          </a:r>
+          <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100">
+            <a:latin typeface="+mn-ea"/>
+            <a:ea typeface="+mn-ea"/>
+          </a:endParaRPr>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
 </xdr:wsDr>
 </file>
 
@@ -2202,56 +1755,6 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>27</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>15</xdr:col>
-      <xdr:colOff>457200</xdr:colOff>
-      <xdr:row>35</xdr:row>
-      <xdr:rowOff>169194</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="7" name="図 6">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{D15F78EC-A612-4060-8841-1FB5B703628C}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3" cstate="print">
-          <a:extLst>
-            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
-              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
-            </a:ext>
-          </a:extLst>
-        </a:blip>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="685800" y="4629150"/>
-          <a:ext cx="10058400" cy="1540794"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
       <xdr:col>17</xdr:col>
       <xdr:colOff>1</xdr:colOff>
       <xdr:row>26</xdr:row>
@@ -2277,7 +1780,7 @@
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId4">
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3">
           <a:extLst>
             <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
               <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
@@ -2292,56 +1795,6 @@
         <a:xfrm>
           <a:off x="11658601" y="4629149"/>
           <a:ext cx="3952874" cy="5656699"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>61</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>15</xdr:col>
-      <xdr:colOff>457200</xdr:colOff>
-      <xdr:row>70</xdr:row>
-      <xdr:rowOff>52772</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="11" name="図 10">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{BC555D75-4D62-4A25-AFE0-0AD32F937B40}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId5" cstate="print">
-          <a:extLst>
-            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
-              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
-            </a:ext>
-          </a:extLst>
-        </a:blip>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="685800" y="10458450"/>
-          <a:ext cx="10058400" cy="1595822"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -2476,130 +1929,6 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>4</xdr:col>
-      <xdr:colOff>390525</xdr:colOff>
-      <xdr:row>31</xdr:row>
-      <xdr:rowOff>28575</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>5</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>32</xdr:row>
-      <xdr:rowOff>85725</xdr:rowOff>
-    </xdr:to>
-    <xdr:sp macro="" textlink="">
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="18" name="正方形/長方形 17">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{3B0D2B3B-6A44-4430-BD1F-35A060DAAA47}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvSpPr/>
-      </xdr:nvSpPr>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="3133725" y="5343525"/>
-          <a:ext cx="295275" cy="228600"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-        <a:ln w="38100" cap="flat" cmpd="sng" algn="ctr">
-          <a:solidFill>
-            <a:srgbClr val="FF0000"/>
-          </a:solidFill>
-          <a:prstDash val="solid"/>
-          <a:round/>
-          <a:headEnd type="none" w="med" len="med"/>
-          <a:tailEnd type="none" w="med" len="med"/>
-        </a:ln>
-      </xdr:spPr>
-      <xdr:style>
-        <a:lnRef idx="0">
-          <a:scrgbClr r="0" g="0" b="0"/>
-        </a:lnRef>
-        <a:fillRef idx="0">
-          <a:scrgbClr r="0" g="0" b="0"/>
-        </a:fillRef>
-        <a:effectRef idx="0">
-          <a:scrgbClr r="0" g="0" b="0"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="accent2"/>
-        </a:fontRef>
-      </xdr:style>
-      <xdr:txBody>
-        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
-        <a:lstStyle/>
-        <a:p>
-          <a:pPr algn="l"/>
-          <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
-        </a:p>
-      </xdr:txBody>
-    </xdr:sp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>4</xdr:col>
-      <xdr:colOff>542925</xdr:colOff>
-      <xdr:row>33</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>4</xdr:col>
-      <xdr:colOff>552450</xdr:colOff>
-      <xdr:row>60</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:to>
-    <xdr:cxnSp macro="">
-      <xdr:nvCxnSpPr>
-        <xdr:cNvPr id="19" name="直線矢印コネクタ 18">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{2EE743A1-5D21-49F6-B0E9-F1E755F35648}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvCxnSpPr/>
-      </xdr:nvCxnSpPr>
-      <xdr:spPr>
-        <a:xfrm flipH="1">
-          <a:off x="3286125" y="5657850"/>
-          <a:ext cx="9525" cy="4629150"/>
-        </a:xfrm>
-        <a:prstGeom prst="straightConnector1">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:ln w="38100">
-          <a:solidFill>
-            <a:srgbClr val="FF0000"/>
-          </a:solidFill>
-          <a:tailEnd type="triangle"/>
-        </a:ln>
-      </xdr:spPr>
-      <xdr:style>
-        <a:lnRef idx="1">
-          <a:schemeClr val="accent1"/>
-        </a:lnRef>
-        <a:fillRef idx="0">
-          <a:schemeClr val="accent1"/>
-        </a:fillRef>
-        <a:effectRef idx="0">
-          <a:schemeClr val="accent1"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="tx1"/>
-        </a:fontRef>
-      </xdr:style>
-    </xdr:cxnSp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
       <xdr:col>7</xdr:col>
       <xdr:colOff>127395</xdr:colOff>
       <xdr:row>24</xdr:row>
@@ -2779,105 +2108,54 @@
     </xdr:sp>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
-      <xdr:col>6</xdr:col>
-      <xdr:colOff>422673</xdr:colOff>
-      <xdr:row>59</xdr:row>
-      <xdr:rowOff>95249</xdr:rowOff>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>684609</xdr:colOff>
+      <xdr:row>27</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>10</xdr:col>
-      <xdr:colOff>226219</xdr:colOff>
-      <xdr:row>62</xdr:row>
-      <xdr:rowOff>41672</xdr:rowOff>
+      <xdr:col>15</xdr:col>
+      <xdr:colOff>473868</xdr:colOff>
+      <xdr:row>43</xdr:row>
+      <xdr:rowOff>5052</xdr:rowOff>
     </xdr:to>
-    <xdr:sp macro="" textlink="">
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="23" name="吹き出し: 四角形 22">
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="4" name="図 3">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{FA27B56E-0DB5-4489-8ECF-0A1AF4AA4831}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{86F2B97D-AD6B-48EF-9637-64A3035653D1}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
-        <xdr:cNvSpPr/>
-      </xdr:nvSpPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId4">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="4530329" y="10281046"/>
-          <a:ext cx="2541984" cy="464345"/>
+          <a:off x="684609" y="4661297"/>
+          <a:ext cx="10058400" cy="2767302"/>
         </a:xfrm>
-        <a:prstGeom prst="wedgeRectCallout">
-          <a:avLst>
-            <a:gd name="adj1" fmla="val -34875"/>
-            <a:gd name="adj2" fmla="val 106346"/>
-          </a:avLst>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
         </a:prstGeom>
       </xdr:spPr>
-      <xdr:style>
-        <a:lnRef idx="2">
-          <a:schemeClr val="accent1"/>
-        </a:lnRef>
-        <a:fillRef idx="1">
-          <a:schemeClr val="lt1"/>
-        </a:fillRef>
-        <a:effectRef idx="0">
-          <a:schemeClr val="accent1"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="dk1"/>
-        </a:fontRef>
-      </xdr:style>
-      <xdr:txBody>
-        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
-        <a:lstStyle/>
-        <a:p>
-          <a:pPr algn="l"/>
-          <a:r>
-            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100"/>
-            <a:t>NO8.</a:t>
-          </a:r>
-          <a:r>
-            <a:rPr lang="ja-JP" altLang="ja-JP" sz="1100">
-              <a:solidFill>
-                <a:schemeClr val="dk1"/>
-              </a:solidFill>
-              <a:effectLst/>
-              <a:latin typeface="+mn-lt"/>
-              <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="+mn-cs"/>
-            </a:rPr>
-            <a:t>戻るボタンを押下して</a:t>
-          </a:r>
-          <a:r>
-            <a:rPr lang="ja-JP" altLang="en-US" sz="1100">
-              <a:solidFill>
-                <a:schemeClr val="dk1"/>
-              </a:solidFill>
-              <a:effectLst/>
-              <a:latin typeface="+mn-lt"/>
-              <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="+mn-cs"/>
-            </a:rPr>
-            <a:t>加入者情報</a:t>
-          </a:r>
-          <a:r>
-            <a:rPr lang="ja-JP" altLang="ja-JP" sz="1100">
-              <a:solidFill>
-                <a:schemeClr val="dk1"/>
-              </a:solidFill>
-              <a:effectLst/>
-              <a:latin typeface="+mn-lt"/>
-              <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="+mn-cs"/>
-            </a:rPr>
-            <a:t>検索画面に戻れる</a:t>
-          </a:r>
-          <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
-        </a:p>
-      </xdr:txBody>
-    </xdr:sp>
+    </xdr:pic>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
 </xdr:wsDr>
@@ -3204,36 +2482,26 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{54B445FB-F118-47FF-BCA2-B773627F0ED9}">
-  <dimension ref="B2:B45"/>
+  <dimension ref="B2:B44"/>
   <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <sheetData>
     <row r="2" spans="2:2" x14ac:dyDescent="0.15">
       <c r="B2" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3" spans="2:2" x14ac:dyDescent="0.15">
       <c r="B3" t="s">
-        <v>0</v>
+        <v>8</v>
       </c>
     </row>
-    <row r="18" spans="2:2" x14ac:dyDescent="0.15">
-      <c r="B18" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="31" spans="2:2" x14ac:dyDescent="0.15">
-      <c r="B31" t="s">
-        <v>4</v>
+    <row r="6" spans="2:2" x14ac:dyDescent="0.15">
+      <c r="B6" t="s">
+        <v>9</v>
       </c>
     </row>
     <row r="44" spans="2:2" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B44" s="2"/>
-    </row>
-    <row r="45" spans="2:2" x14ac:dyDescent="0.15">
-      <c r="B45" t="s">
-        <v>8</v>
-      </c>
     </row>
   </sheetData>
   <phoneticPr fontId="1"/>
@@ -3254,15 +2522,15 @@
     <row r="1" spans="2:39" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
     <row r="2" spans="2:39" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B2" t="s">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AM2" t="s">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="26" spans="39:39" x14ac:dyDescent="0.15">
       <c r="AM26" t="s">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
   </sheetData>
@@ -3280,15 +2548,15 @@
   <sheetData>
     <row r="2" spans="2:18" x14ac:dyDescent="0.15">
       <c r="B2" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="R2" t="s">
-        <v>6</v>
+        <v>3</v>
       </c>
     </row>
     <row r="26" spans="18:18" x14ac:dyDescent="0.15">
       <c r="R26" t="s">
-        <v>6</v>
+        <v>3</v>
       </c>
     </row>
   </sheetData>
@@ -3305,15 +2573,15 @@
   <sheetData>
     <row r="2" spans="2:18" x14ac:dyDescent="0.15">
       <c r="B2" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="R2" t="s">
-        <v>7</v>
+        <v>4</v>
       </c>
     </row>
     <row r="25" spans="18:18" x14ac:dyDescent="0.15">
       <c r="R25" t="s">
-        <v>7</v>
+        <v>4</v>
       </c>
     </row>
   </sheetData>
@@ -3330,10 +2598,10 @@
   <sheetData>
     <row r="2" spans="2:18" x14ac:dyDescent="0.15">
       <c r="B2" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="R2" t="s">
-        <v>7</v>
+        <v>4</v>
       </c>
     </row>
     <row r="16" spans="2:18" x14ac:dyDescent="0.15">
@@ -3341,7 +2609,7 @@
     </row>
     <row r="26" spans="18:18" x14ac:dyDescent="0.15">
       <c r="R26" t="s">
-        <v>7</v>
+        <v>4</v>
       </c>
     </row>
   </sheetData>
@@ -3352,21 +2620,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement/>
-</p:properties>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="ドキュメント" ma:contentTypeID="0x010100C424317A42AA8449A97AAE94730ED181" ma:contentTypeVersion="6" ma:contentTypeDescription="新しいドキュメントを作成します。" ma:contentTypeScope="" ma:versionID="9df5c7ff725c9e365f8a8503f6029c6b">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="dab87824-9c6b-4a08-9c96-9c9ea904f12c" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="98e3d8fd3bbedc5b58bd9df00d6be37e" ns2:_="">
     <xsd:import namespace="dab87824-9c6b-4a08-9c96-9c9ea904f12c"/>
@@ -3524,31 +2777,22 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F8048152-0CA9-47E5-A6CC-6D3980A2E781}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="dab87824-9c6b-4a08-9c96-9c9ea904f12c"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{25A96F8A-B775-40FD-BBE8-4BBDAB58FCAE}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
 </file>
 
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{EFE06169-F6B9-4EE2-B032-3DCCE6AFCC5C}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -3564,4 +2808,28 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{25A96F8A-B775-40FD-BBE8-4BBDAB58FCAE}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F8048152-0CA9-47E5-A6CC-6D3980A2E781}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="dab87824-9c6b-4a08-9c96-9c9ea904f12c"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
--- a/extra/report/No.課題2_テスト結果.xlsx
+++ b/extra/report/No.課題2_テスト結果.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="20417"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E9D7578B-7E22-43A5-AF0C-CDAFC901A319}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4EDE807B-1951-463D-A589-87D9CD243A24}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="240" yWindow="105" windowWidth="14805" windowHeight="8010" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1927,18 +1927,68 @@
     </xdr:cxnSp>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>684609</xdr:colOff>
+      <xdr:row>27</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>15</xdr:col>
+      <xdr:colOff>473868</xdr:colOff>
+      <xdr:row>43</xdr:row>
+      <xdr:rowOff>5052</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="4" name="図 3">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{86F2B97D-AD6B-48EF-9637-64A3035653D1}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId4">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="684609" y="4661297"/>
+          <a:ext cx="10058400" cy="2767302"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>7</xdr:col>
-      <xdr:colOff>127395</xdr:colOff>
-      <xdr:row>24</xdr:row>
-      <xdr:rowOff>82155</xdr:rowOff>
+      <xdr:colOff>422670</xdr:colOff>
+      <xdr:row>28</xdr:row>
+      <xdr:rowOff>63105</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>11</xdr:col>
-      <xdr:colOff>458390</xdr:colOff>
-      <xdr:row>29</xdr:row>
-      <xdr:rowOff>107158</xdr:rowOff>
+      <xdr:col>12</xdr:col>
+      <xdr:colOff>67865</xdr:colOff>
+      <xdr:row>33</xdr:row>
+      <xdr:rowOff>88108</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -1953,8 +2003,8 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="4919661" y="4225530"/>
-          <a:ext cx="3069432" cy="888206"/>
+          <a:off x="5223270" y="4863705"/>
+          <a:ext cx="3074195" cy="882253"/>
         </a:xfrm>
         <a:prstGeom prst="wedgeRectCallout">
           <a:avLst>
@@ -2106,56 +2156,6 @@
         </a:p>
       </xdr:txBody>
     </xdr:sp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>684609</xdr:colOff>
-      <xdr:row>27</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>15</xdr:col>
-      <xdr:colOff>473868</xdr:colOff>
-      <xdr:row>43</xdr:row>
-      <xdr:rowOff>5052</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="4" name="図 3">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{86F2B97D-AD6B-48EF-9637-64A3035653D1}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId4">
-          <a:extLst>
-            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
-              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
-            </a:ext>
-          </a:extLst>
-        </a:blip>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="684609" y="4661297"/>
-          <a:ext cx="10058400" cy="2767302"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
 </xdr:wsDr>
@@ -2620,6 +2620,15 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="ドキュメント" ma:contentTypeID="0x010100C424317A42AA8449A97AAE94730ED181" ma:contentTypeVersion="6" ma:contentTypeDescription="新しいドキュメントを作成します。" ma:contentTypeScope="" ma:versionID="9df5c7ff725c9e365f8a8503f6029c6b">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="dab87824-9c6b-4a08-9c96-9c9ea904f12c" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="98e3d8fd3bbedc5b58bd9df00d6be37e" ns2:_="">
     <xsd:import namespace="dab87824-9c6b-4a08-9c96-9c9ea904f12c"/>
@@ -2777,15 +2786,6 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement/>
@@ -2793,6 +2793,14 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{25A96F8A-B775-40FD-BBE8-4BBDAB58FCAE}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{EFE06169-F6B9-4EE2-B032-3DCCE6AFCC5C}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -2806,14 +2814,6 @@
     <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
     <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{25A96F8A-B775-40FD-BBE8-4BBDAB58FCAE}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
